--- a/artfynd/A 44914-2021 artfynd.xlsx
+++ b/artfynd/A 44914-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44914-2021 artfynd.xlsx
+++ b/artfynd/A 44914-2021 artfynd.xlsx
@@ -3231,7 +3231,7 @@
         <v>122753482</v>
       </c>
       <c r="B25" t="n">
-        <v>78499</v>
+        <v>78503</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 44914-2021 artfynd.xlsx
+++ b/artfynd/A 44914-2021 artfynd.xlsx
@@ -3231,7 +3231,7 @@
         <v>122753482</v>
       </c>
       <c r="B25" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 44914-2021 artfynd.xlsx
+++ b/artfynd/A 44914-2021 artfynd.xlsx
@@ -3231,7 +3231,7 @@
         <v>122753482</v>
       </c>
       <c r="B25" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 44914-2021 artfynd.xlsx
+++ b/artfynd/A 44914-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680272</v>
+        <v>113680258</v>
       </c>
       <c r="B2" t="n">
-        <v>93208</v>
+        <v>93259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506039</v>
+        <v>505983</v>
       </c>
       <c r="R2" t="n">
-        <v>7130889</v>
+        <v>7130808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680256</v>
+        <v>113679015</v>
       </c>
       <c r="B3" t="n">
-        <v>93198</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505984</v>
+        <v>505996</v>
       </c>
       <c r="R3" t="n">
-        <v>7130854</v>
+        <v>7130842</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,12 +863,12 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680260</v>
+        <v>113679018</v>
       </c>
       <c r="B4" t="n">
-        <v>93216</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505984</v>
+        <v>506045</v>
       </c>
       <c r="R4" t="n">
-        <v>7130806</v>
+        <v>7130877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,12 +969,12 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680268</v>
+        <v>113680267</v>
       </c>
       <c r="B5" t="n">
-        <v>93204</v>
+        <v>93287</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506047</v>
+        <v>506036</v>
       </c>
       <c r="R5" t="n">
-        <v>7130889</v>
+        <v>7130879</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,45 +1099,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680271</v>
+        <v>113680273</v>
       </c>
       <c r="B6" t="n">
-        <v>93222</v>
+        <v>93287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>slåtten, Jmt</t>
+          <t>Långnäsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506039</v>
+        <v>506054</v>
       </c>
       <c r="R6" t="n">
-        <v>7130882</v>
+        <v>7130957</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680267</v>
+        <v>113680263</v>
       </c>
       <c r="B7" t="n">
-        <v>93220</v>
+        <v>93263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506036</v>
+        <v>506011</v>
       </c>
       <c r="R7" t="n">
-        <v>7130879</v>
+        <v>7130830</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113680255</v>
+        <v>113680269</v>
       </c>
       <c r="B8" t="n">
-        <v>93216</v>
+        <v>93263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505993</v>
+        <v>506038</v>
       </c>
       <c r="R8" t="n">
-        <v>7130928</v>
+        <v>7130884</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113680269</v>
+        <v>113680270</v>
       </c>
       <c r="B9" t="n">
-        <v>93196</v>
+        <v>93263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506038</v>
+        <v>506037</v>
       </c>
       <c r="R9" t="n">
-        <v>7130884</v>
+        <v>7130879</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,32 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113680264</v>
+        <v>113680256</v>
       </c>
       <c r="B10" t="n">
-        <v>93216</v>
+        <v>93265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506014</v>
+        <v>505984</v>
       </c>
       <c r="R10" t="n">
-        <v>7130830</v>
+        <v>7130854</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680270</v>
+        <v>113680261</v>
       </c>
       <c r="B11" t="n">
-        <v>93196</v>
+        <v>93265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506037</v>
+        <v>505981</v>
       </c>
       <c r="R11" t="n">
-        <v>7130879</v>
+        <v>7130808</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680261</v>
+        <v>113680262</v>
       </c>
       <c r="B12" t="n">
-        <v>93198</v>
+        <v>93265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505981</v>
+        <v>506011</v>
       </c>
       <c r="R12" t="n">
-        <v>7130808</v>
+        <v>7130828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,32 +1841,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680257</v>
+        <v>113680265</v>
       </c>
       <c r="B13" t="n">
-        <v>93216</v>
+        <v>93271</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505985</v>
+        <v>506014</v>
       </c>
       <c r="R13" t="n">
-        <v>7130854</v>
+        <v>7130833</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,14 +1947,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113680265</v>
+        <v>113680268</v>
       </c>
       <c r="B14" t="n">
-        <v>93204</v>
+        <v>93271</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506014</v>
+        <v>506047</v>
       </c>
       <c r="R14" t="n">
-        <v>7130833</v>
+        <v>7130889</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,32 +2053,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113680266</v>
+        <v>113680272</v>
       </c>
       <c r="B15" t="n">
-        <v>93216</v>
+        <v>93275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506023</v>
+        <v>506039</v>
       </c>
       <c r="R15" t="n">
-        <v>7130842</v>
+        <v>7130889</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,32 +2159,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113677109</v>
+        <v>113680254</v>
       </c>
       <c r="B16" t="n">
-        <v>5199</v>
+        <v>93283</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506038</v>
+        <v>506000</v>
       </c>
       <c r="R16" t="n">
-        <v>7130869</v>
+        <v>7130928</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,12 +2241,12 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW16" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113680263</v>
+        <v>113680255</v>
       </c>
       <c r="B17" t="n">
-        <v>93196</v>
+        <v>93283</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506011</v>
+        <v>505993</v>
       </c>
       <c r="R17" t="n">
-        <v>7130830</v>
+        <v>7130928</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,48 +2371,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113680259</v>
+        <v>113680257</v>
       </c>
       <c r="B18" t="n">
-        <v>93217</v>
+        <v>93283</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>232140</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>slåtten, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505988</v>
+        <v>505985</v>
       </c>
       <c r="R18" t="n">
-        <v>7130812</v>
+        <v>7130854</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,11 +2450,15 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW18" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2476,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113679017</v>
+        <v>113680260</v>
       </c>
       <c r="B19" t="n">
-        <v>79332</v>
+        <v>93283</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,21 +2488,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2511,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506035</v>
+        <v>505984</v>
       </c>
       <c r="R19" t="n">
-        <v>7130869</v>
+        <v>7130806</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,12 +2559,12 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW19" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2582,14 +2583,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113680254</v>
+        <v>113680264</v>
       </c>
       <c r="B20" t="n">
-        <v>93216</v>
+        <v>93283</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2617,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506000</v>
+        <v>506014</v>
       </c>
       <c r="R20" t="n">
-        <v>7130928</v>
+        <v>7130830</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113680262</v>
+        <v>113680266</v>
       </c>
       <c r="B21" t="n">
-        <v>93198</v>
+        <v>93283</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2700,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506011</v>
+        <v>506023</v>
       </c>
       <c r="R21" t="n">
-        <v>7130828</v>
+        <v>7130842</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113679015</v>
+        <v>113680271</v>
       </c>
       <c r="B22" t="n">
-        <v>78998</v>
+        <v>93289</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>4368</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2829,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>505996</v>
+        <v>506039</v>
       </c>
       <c r="R22" t="n">
-        <v>7130842</v>
+        <v>7130882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,12 +2877,12 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW22" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2900,32 +2901,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113679018</v>
+        <v>113679017</v>
       </c>
       <c r="B23" t="n">
-        <v>78998</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2935,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506045</v>
+        <v>506035</v>
       </c>
       <c r="R23" t="n">
-        <v>7130877</v>
+        <v>7130869</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3006,32 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113680258</v>
+        <v>113677109</v>
       </c>
       <c r="B24" t="n">
-        <v>93192</v>
+        <v>5201</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>149</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3041,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>505983</v>
+        <v>506038</v>
       </c>
       <c r="R24" t="n">
-        <v>7130808</v>
+        <v>7130869</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,12 +3089,12 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW24" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3115,12 +3116,7 @@
         <v>122753482</v>
       </c>
       <c r="B25" t="n">
-        <v>78508</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3208,112 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>113680259</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93302</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>slåtten, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>505988</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7130812</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 44914-2021 artfynd.xlsx
+++ b/artfynd/A 44914-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680258</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679015</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679018</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680267</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680273</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680263</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680269</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680270</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680256</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680261</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680262</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680265</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680268</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680272</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680254</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680255</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680257</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2580,6 +2670,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680260</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2686,6 +2781,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680264</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680266</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2898,6 +3003,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680271</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3004,6 +3114,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679017</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3110,6 +3225,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113677109</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3209,6 +3329,11 @@
       <c r="AY25" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122753482</t>
         </is>
       </c>
     </row>
@@ -3316,8 +3441,40 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>